--- a/public/adoption-plan-empty.xlsx
+++ b/public/adoption-plan-empty.xlsx
@@ -6,16 +6,16 @@
     <sheet state="visible" name="INSTRUCTIONS" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="PS Use Case Worksheet" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="Stream Overview" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="wgdefault" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="wgdefaultHybrid" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="wg-default" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="wg-defaultHybrid" sheetId="5" r:id="rId9"/>
     <sheet state="visible" name="Edge Overview" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="fldefault_fleet" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="fl-default" sheetId="7" r:id="rId11"/>
     <sheet state="visible" name="input_data" sheetId="8" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">wgdefault!$A$2:$AE$21</definedName>
-    <definedName hidden="1" localSheetId="4" name="_xlnm._FilterDatabase">wgdefaultHybrid!$A$2:$AE$21</definedName>
-    <definedName hidden="1" localSheetId="6" name="_xlnm._FilterDatabase">fldefault_fleet!$A$2:$AE$21</definedName>
+    <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">'wg-default'!$A$2:$AE$21</definedName>
+    <definedName hidden="1" localSheetId="4" name="_xlnm._FilterDatabase">'wg-defaultHybrid'!$A$2:$AE$21</definedName>
+    <definedName hidden="1" localSheetId="6" name="_xlnm._FilterDatabase">'fl-default'!$A$2:$AE$21</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
@@ -2159,6 +2159,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
@@ -2220,6 +2221,9 @@
     <mergeCell ref="B7:L7"/>
     <mergeCell ref="B8:L8"/>
   </mergeCells>
+  <printOptions gridLines="1" horizontalCentered="1"/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup fitToHeight="0" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3203,7 +3207,7 @@
     <col customWidth="1" min="3" max="3" width="18.63" outlineLevel="1"/>
     <col customWidth="1" min="4" max="4" width="15.25" outlineLevel="1"/>
     <col customWidth="1" min="5" max="5" width="13.75"/>
-    <col collapsed="1" customWidth="1" min="6" max="6" width="11.75"/>
+    <col customWidth="1" hidden="1" min="6" max="6" width="11.75"/>
     <col customWidth="1" min="7" max="7" width="14.75" outlineLevel="1"/>
     <col customWidth="1" min="8" max="9" width="32.13" outlineLevel="1"/>
     <col customWidth="1" min="10" max="10" width="11.75" outlineLevel="1"/>
